--- a/5/search/FY2_Missile3_results/all_solutions.xlsx
+++ b/5/search/FY2_Missile3_results/all_solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,142 +487,562 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>252</v>
+        <v>207</v>
       </c>
       <c r="B2" t="n">
-        <v>103.6</v>
+        <v>124</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>11615.83007259307</v>
+        <v>9790.303820012847</v>
       </c>
       <c r="F2" t="n">
-        <v>217.6465389418652</v>
+        <v>274.1035606459243</v>
       </c>
       <c r="G2" t="n">
         <v>1400</v>
       </c>
       <c r="H2" t="n">
-        <v>11423.7451088896</v>
+        <v>8685.45573001927</v>
       </c>
       <c r="I2" t="n">
-        <v>-373.5301915872022</v>
+        <v>-288.8446590311136</v>
       </c>
       <c r="J2" t="n">
-        <v>1223.6</v>
+        <v>910</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="B3" t="n">
-        <v>131.6</v>
+        <v>102</v>
       </c>
       <c r="C3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" t="n">
         <v>8</v>
       </c>
-      <c r="D3" t="n">
-        <v>6</v>
-      </c>
       <c r="E3" t="n">
-        <v>11674.66690832205</v>
+        <v>10846.00173310355</v>
       </c>
       <c r="F3" t="n">
-        <v>398.7276996444624</v>
+        <v>246.0017331035544</v>
       </c>
       <c r="G3" t="n">
         <v>1400</v>
       </c>
       <c r="H3" t="n">
-        <v>11430.6670895636</v>
+        <v>10269.00259965533</v>
       </c>
       <c r="I3" t="n">
-        <v>-352.2265256221908</v>
+        <v>-330.9974003446683</v>
       </c>
       <c r="J3" t="n">
-        <v>1223.6</v>
+        <v>1086.4</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8000000000000007</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="B4" t="n">
-        <v>106.4</v>
+        <v>122</v>
       </c>
       <c r="C4" t="n">
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>12000</v>
+        <v>10964.79567234289</v>
       </c>
       <c r="F4" t="n">
-        <v>123.1999999999998</v>
+        <v>364.7956723428947</v>
       </c>
       <c r="G4" t="n">
         <v>1400</v>
       </c>
       <c r="H4" t="n">
-        <v>12000</v>
+        <v>10274.65945390482</v>
       </c>
       <c r="I4" t="n">
-        <v>-408.8000000000002</v>
+        <v>-325.3405460951756</v>
       </c>
       <c r="J4" t="n">
-        <v>1277.5</v>
+        <v>1086.4</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2000000000000028</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108</v>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11322.84186012813</v>
+      </c>
+      <c r="F5" t="n">
+        <v>294.9783469970962</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10927.83294520287</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-349.6176172545977</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1159.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>136</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11431.52156158905</v>
+      </c>
+      <c r="F6" t="n">
+        <v>472.3275011827475</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10934.10292797947</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-339.3859352823484</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1159.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>252</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>11614.34679102007</v>
+      </c>
+      <c r="F7" t="n">
+        <v>213.0814676636485</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11421.5201865301</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-380.3777985045273</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>252</v>
+      </c>
+      <c r="B8" t="n">
+        <v>132</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11673.67805394006</v>
+      </c>
+      <c r="F8" t="n">
+        <v>395.6843187923179</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H8" t="n">
+        <v>11428.9365943951</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-357.5524421134437</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>252</v>
+      </c>
+      <c r="B9" t="n">
+        <v>134</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>11668.73378203006</v>
+      </c>
+      <c r="F9" t="n">
+        <v>380.4674145315954</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11420.2841185526</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-384.182024569708</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>256.5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>102</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>11714.26287464037</v>
+      </c>
+      <c r="F10" t="n">
+        <v>209.8192174332437</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11571.39431196056</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-385.2711738501345</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>265.5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>138</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11913.38115831646</v>
+      </c>
+      <c r="F11" t="n">
+        <v>299.4032635586268</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H11" t="n">
+        <v>11859.24438226425</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-388.4696967172315</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>270</v>
       </c>
-      <c r="B5" t="n">
-        <v>137.2</v>
-      </c>
-      <c r="C5" t="n">
+      <c r="B12" t="n">
+        <v>106</v>
+      </c>
+      <c r="C12" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F12" t="n">
+        <v>128</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-402</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>270</v>
+      </c>
+      <c r="B13" t="n">
+        <v>136</v>
+      </c>
+      <c r="C13" t="n">
         <v>8</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E13" t="n">
         <v>12000</v>
       </c>
-      <c r="F5" t="n">
-        <v>302.4000000000001</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1400</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="F13" t="n">
+        <v>312</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H13" t="n">
         <v>12000</v>
       </c>
-      <c r="I5" t="n">
-        <v>-383.5999999999999</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="I13" t="n">
+        <v>-368</v>
+      </c>
+      <c r="J13" t="n">
         <v>1277.5</v>
       </c>
-      <c r="K5" t="n">
-        <v>3.700000000000001</v>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>270</v>
+      </c>
+      <c r="B14" t="n">
+        <v>138</v>
+      </c>
+      <c r="C14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F14" t="n">
+        <v>296</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-394</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>274.5</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106</v>
+      </c>
+      <c r="C15" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12099.79996976582</v>
+      </c>
+      <c r="F15" t="n">
+        <v>131.9211514914612</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12141.38329050158</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-396.4450353870967</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C16" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12324.95594648742</v>
+      </c>
+      <c r="F16" t="n">
+        <v>46.46107080643424</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12433.27459531656</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-404.7185722580877</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1321.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="B17" t="n">
+        <v>132</v>
+      </c>
+      <c r="C17" t="n">
+        <v>12</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>12606.1705568663</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-63.42517949787793</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12757.71319608288</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-429.2814743723474</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1355.9</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
